--- a/Problem7_Early_Warning_System/reports/financial_impact_reporting_packaging/AMEX_Problem7_Financial_Impact_Workbook.xlsx
+++ b/Problem7_Early_Warning_System/reports/financial_impact_reporting_packaging/AMEX_Problem7_Financial_Impact_Workbook.xlsx
@@ -78,7 +78,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -110,6 +110,11 @@
         <fgColor rgb="00C41E3A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0063BE7B"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -123,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -141,6 +146,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -379,8 +387,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CandidateSweep" displayName="CandidateSweep" ref="A1:I6" headerRowCount="1">
-  <autoFilter ref="A1:I6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CandidateSweep" displayName="CandidateSweep" ref="A1:I10" headerRowCount="1">
+  <autoFilter ref="A1:I10"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Candidate"/>
     <tableColumn id="2" name="N Alerted"/>
@@ -728,7 +736,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>MIN_DEVIATION_COUNT=8  (see Candidate Sweep sheet)</t>
+          <t>MIN_DEVIATION_COUNT=10  (see Candidate Sweep sheet)</t>
         </is>
       </c>
     </row>
@@ -773,7 +781,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>168,865%  (reported, see Section 7)</t>
+          <t>116,386%  (reported, see Section 7)</t>
         </is>
       </c>
     </row>
@@ -795,14 +803,14 @@
           <t>Deployment Status</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>NOT RECOMMENDED for production</t>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>RECOMMENDED for production</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Rows 6-8 recalculate live from the Assumptions and Alert Impact sheets.</t>
         </is>
@@ -840,17 +848,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Source / Rationale</t>
         </is>
@@ -862,10 +870,10 @@
           <t>Ead Per Account Usd</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n">
+      <c r="B2" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Notebook 08 (inherited, real value read programmatically)</t>
         </is>
@@ -877,10 +885,10 @@
           <t>Lgd Assumption</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="14" t="n">
         <v>0.45</v>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Notebook 08 (inherited, real value read programmatically)</t>
         </is>
@@ -892,10 +900,10 @@
           <t>Alert Intervention Success Rate</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B4" s="14" t="n">
         <v>0.15</v>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>ASSUMPTION -- illustrative efficacy of a lightweight early-warning-triggered check-in (a proactive phone/email outreach or a soft credit-line freeze) on an account whose LATEST statement deviated from its own recent baseline; set lower than Problem 6's 20% recency-model assumption since an early-warning alert is a much lighter-touch signal (a statistical deviation, not a trained model's calibrated PD) -- edit to your institution's own outcome data.</t>
         </is>
@@ -907,10 +915,10 @@
           <t>False Positive Review Cost Usd</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>ASSUMPTION -- illustrative staff-time cost of a quick triage check on one account this technique flags that does NOT go on to default -- set lower than Problem 6's $35 assumption because an early-warning alert review is a fast automated-then-human triage step, not a full account re-underwrite; edit to your institution's actual cost.</t>
         </is>
@@ -922,10 +930,10 @@
           <t>Implementation Cost Usd</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>ASSUMPTION -- illustrative one-time build/validate/deploy cost for the real-time alert service; set lower than Problem 6's $60,000 since this is a stateless, rule-based service (no model training/retraining pipeline to build or maintain) -- edit to your institution's actual project cost.</t>
         </is>
@@ -937,10 +945,10 @@
           <t>Annual Application Cycles</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>ASSUMPTION -- monthly re-scoring cadence, matching Problem 6's own monitoring cadence (both are statement-driven, ongoing existing-book monitoring signals, unlike Problem 5's quarterly new-account screening cadence); edit to your institution's actual cadence.</t>
         </is>
@@ -968,12 +976,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -986,7 +994,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1016,7 +1024,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13584</v>
+        <v>9171</v>
       </c>
     </row>
     <row r="6">
@@ -1026,7 +1034,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24091</v>
+        <v>12257</v>
       </c>
     </row>
     <row r="7">
@@ -1035,8 +1043,8 @@
           <t>Real Defaulter Capture Rate</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
-        <v>0.5999734994037366</v>
+      <c r="B7" s="16" t="n">
+        <v>0.4050616138863125</v>
       </c>
     </row>
     <row r="8">
@@ -1056,7 +1064,7 @@
           <t>Gross Loss Prevented / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="17">
         <f>B8*Assumptions!$B$2*Assumptions!$B$3</f>
         <v/>
       </c>
@@ -1067,7 +1075,7 @@
           <t>False-Positive Review Cost / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="17">
         <f>B6*Assumptions!$B$5</f>
         <v/>
       </c>
@@ -1078,7 +1086,7 @@
           <t>Net Benefit / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="17">
         <f>B9-B10</f>
         <v/>
       </c>
@@ -1089,7 +1097,7 @@
           <t>Annual Net Benefit (USD)</t>
         </is>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="17">
         <f>B11*Assumptions!$B$7</f>
         <v/>
       </c>
@@ -1109,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1124,47 +1132,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Candidate</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>N Alerted</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>% Alerted</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Default Rate Lift</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Meets KPI</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>MCC</t>
         </is>
@@ -1177,10 +1185,10 @@
       <c r="B2" t="n">
         <v>88192</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>0.9977712158752786</v>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="19" t="n">
         <v>1.001127104686779</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -1208,10 +1216,10 @@
       <c r="B3" t="n">
         <v>87045</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <v>0.9847944880019007</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="19" t="n">
         <v>1.008174650757145</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -1239,10 +1247,10 @@
       <c r="B4" t="n">
         <v>84127</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>0.9517813302560273</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="19" t="n">
         <v>1.026994817090138</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -1270,10 +1278,10 @@
       <c r="B5" t="n">
         <v>69466</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>0.7859122741517609</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="19" t="n">
         <v>1.122129918301476</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -1301,10 +1309,10 @@
       <c r="B6" t="n">
         <v>37675</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>0.4262408218217199</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="19" t="n">
         <v>1.407592770770985</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,6 +1331,130 @@
       </c>
       <c r="I6" t="n">
         <v>0.2061558670548354</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B7" t="n">
+        <v>21428</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>0.2424283564696965</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>1.670850802211932</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4279914131043495</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4050616138863125</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4162109419319703</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2226959536289439</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B8" t="n">
+        <v>11183</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>0.126520268359185</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>1.950396739376873</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4995976035053206</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2467647188728413</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3303571428571428</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2122585059508088</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3783</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>0.04279944336965007</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>2.254850307882919</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.577583928099392</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.096506338059273</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.16537995761429</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1557098333294085</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B10" t="n">
+        <v>462</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>0.005226894749346638</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>2.619523712010793</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.670995670995671</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01369197473609823</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.02683634160065792</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.06888960587762505</v>
       </c>
     </row>
   </sheetData>
@@ -1347,12 +1479,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Org Level</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Suggestion</t>
         </is>
@@ -1364,9 +1496,9 @@
           <t>Behavioral Monitoring Ops / Frontline Risk Analysts</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>Work the 37,675-account alert list from the real-time early warning service (candidate MIN_DEVIATION_COUNT=8, 60.0% real defaulter capture) as new statements land -- this is a per-statement, near-real-time signal (not a monthly batch score), so route alerts to same-week outreach, not end-of-cycle review.</t>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Work the 21,428-account alert list from the real-time early warning service (candidate MIN_DEVIATION_COUNT=10, 40.5% real defaulter capture) as new statements land -- this is a per-statement, near-real-time signal (not a monthly batch score), so route alerts to same-week outreach, not end-of-cycle review.</t>
         </is>
       </c>
     </row>
@@ -1376,9 +1508,9 @@
           <t>Portfolio Risk Team Lead</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>Track the 2,038-account intervention goal (from the 15% ASSUMPTION success rate) and the 24,091 real false positives (review-cost exposure) as paired weekly KPIs, exactly as Problem 6 tracks its own pair -- both platforms' thresholds trade the same true-positive/false-positive tension, just via different mechanisms (a trained model's threshold vs. this technique's deviation-count threshold).</t>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Track the 1,376-account intervention goal (from the 15% ASSUMPTION success rate) and the 12,257 real false positives (review-cost exposure) as paired weekly KPIs, exactly as Problem 6 tracks its own pair -- both platforms' thresholds trade the same true-positive/false-positive tension, just via different mechanisms (a trained model's threshold vs. this technique's deviation-count threshold).</t>
         </is>
       </c>
     </row>
@@ -1388,9 +1520,9 @@
           <t>Risk / Credit Analyst</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Monitor the real default-rate lift (1.41x, 95% CI [1.39x, 1.42x]) and the split-half score PSI (0.0002) every cycle -- a small alerted population (42.62% of holdout) makes the lift point estimate sensitive to individual customers, which is exactly why the bootstrap CI (not just the point estimate) is the number to watch for drift.</t>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Monitor the real default-rate lift (1.67x, 95% CI [1.65x, 1.69x]) and the split-half score PSI (0.0002) every cycle -- a small alerted population (24.24% of holdout) makes the lift point estimate sensitive to individual customers, which is exactly why the bootstrap CI (not just the point estimate) is the number to watch for drift.</t>
         </is>
       </c>
     </row>
@@ -1400,9 +1532,9 @@
           <t>Model Risk / Compliance (SR 11-7)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>File Notebook 44's bootstrap lift/AUC CIs, score-rank calibration monotonicity (True), and lift-KPI result (NOT MET) with the technique's annual governance packet; note this is an unsupervised, rule-based statistical-process-control technique, not a trained classifier, so its governance review should assess policy-parameter stability (Z_THRESHOLD, MIN_DEVIATION_COUNT), not model retraining cadence. Currently NOT RECOMMENDED for production.</t>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>File Notebook 44's bootstrap lift/AUC CIs, score-rank calibration monotonicity (True), and lift-KPI result (MET) with the technique's annual governance packet; note this is an unsupervised, rule-based statistical-process-control technique, not a trained classifier, so its governance review should assess policy-parameter stability (Z_THRESHOLD, MIN_DEVIATION_COUNT), not model retraining cadence. Currently RECOMMENDED for production.</t>
         </is>
       </c>
     </row>
@@ -1412,9 +1544,9 @@
           <t>Finance / Provisioning Team</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Use the 13,584 alert-flagged real defaulters to trigger EARLY, same-cycle reserve-timing reviews on accounts whose deviation from their own baseline may predate what Problem 6's recency model or Problem 1's full-history model would flag -- coordinate with Problem 3's ECL work and Problem 4's tier-differentiated LGD for the $ reserve amount per flagged account.</t>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Use the 9,171 alert-flagged real defaulters to trigger EARLY, same-cycle reserve-timing reviews on accounts whose deviation from their own baseline may predate what Problem 6's recency model or Problem 1's full-history model would flag -- coordinate with Problem 3's ECL work and Problem 4's tier-differentiated LGD for the $ reserve amount per flagged account.</t>
         </is>
       </c>
     </row>
@@ -1424,9 +1556,9 @@
           <t>CFO / Executive Leadership</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Approve the $30,000 investment given an estimated 0.0 months payback and 168,865% Year-1 ROI (net of estimated false-positive review cost) from monthly-equivalent alert triage; note this technique's lower implementation cost than Problem 6's ($30,000 vs. Problem 6's assumption) reflects its stateless, rule-based nature -- no model training/retraining pipeline to build.</t>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Approve the $30,000 investment given an estimated 0.0 months payback and 116,386% Year-1 ROI (net of estimated false-positive review cost) from monthly-equivalent alert triage; note this technique's lower implementation cost than Problem 6's ($30,000 vs. Problem 6's assumption) reflects its stateless, rule-based nature -- no model training/retraining pipeline to build.</t>
         </is>
       </c>
     </row>

--- a/Problem7_Early_Warning_System/reports/financial_impact_reporting_packaging/AMEX_Problem7_Financial_Impact_Workbook.xlsx
+++ b/Problem7_Early_Warning_System/reports/financial_impact_reporting_packaging/AMEX_Problem7_Financial_Impact_Workbook.xlsx
@@ -21,11 +21,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,6 +76,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -128,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,7 +145,7 @@
     <xf numFmtId="3" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -153,16 +159,24 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -704,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -714,6 +728,7 @@
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -725,6 +740,13 @@
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Comprehensive Financial Impact Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Project Portfolio Prepared By Nandagopal R</t>
         </is>
       </c>
     </row>
@@ -757,7 +779,7 @@
           <t>Net Benefit / Cycle</t>
         </is>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="20">
         <f>'Alert Impact'!B11</f>
         <v/>
       </c>
@@ -870,7 +892,7 @@
           <t>Ead Per Account Usd</t>
         </is>
       </c>
-      <c r="B2" s="12" t="n">
+      <c r="B2" s="21" t="n">
         <v>5000</v>
       </c>
       <c r="C2" s="13" t="inlineStr">
@@ -885,7 +907,7 @@
           <t>Lgd Assumption</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="22" t="n">
         <v>0.45</v>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -900,7 +922,7 @@
           <t>Alert Intervention Success Rate</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="22" t="n">
         <v>0.15</v>
       </c>
       <c r="C4" s="13" t="inlineStr">
@@ -915,7 +937,7 @@
           <t>False Positive Review Cost Usd</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -930,7 +952,7 @@
           <t>Implementation Cost Usd</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="21" t="n">
         <v>30000</v>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -1043,7 +1065,7 @@
           <t>Real Defaulter Capture Rate</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="23" t="n">
         <v>0.4050616138863125</v>
       </c>
     </row>
@@ -1064,7 +1086,7 @@
           <t>Gross Loss Prevented / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="24">
         <f>B8*Assumptions!$B$2*Assumptions!$B$3</f>
         <v/>
       </c>
@@ -1075,7 +1097,7 @@
           <t>False-Positive Review Cost / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="24">
         <f>B6*Assumptions!$B$5</f>
         <v/>
       </c>
@@ -1086,7 +1108,7 @@
           <t>Net Benefit / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="24">
         <f>B9-B10</f>
         <v/>
       </c>
@@ -1097,7 +1119,7 @@
           <t>Annual Net Benefit (USD)</t>
         </is>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="24">
         <f>B11*Assumptions!$B$7</f>
         <v/>
       </c>
